--- a/data/監控股票.xlsx
+++ b/data/監控股票.xlsx
@@ -1,49 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ihsiangtsou-my.sharepoint.com/personal/yihshan_ihsiangtsou_onmicrosoft_com/Documents/每日收盤/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ihsiangtsou-my.sharepoint.com/personal/yihshan_ihsiangtsou_onmicrosoft_com/Documents/GitHub/stock-dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="68" documentId="8_{FE0FB24B-9034-41BB-A0B2-7B438AA1CF4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{99304E13-9C61-419B-B42D-2177F03A5587}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7DB10D0E-727A-4EEA-B726-C4DEB2E7E2B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="2715" windowWidth="29040" windowHeight="15720" xr2:uid="{1272DF0D-3EAB-4F5B-8D61-874287AAEAA6}"/>
+    <workbookView xWindow="-28920" yWindow="2715" windowWidth="29040" windowHeight="15720" xr2:uid="{8896E701-D4C2-4EA3-A0CB-CC938DEDCC47}"/>
   </bookViews>
   <sheets>
-    <sheet name="工作表1" sheetId="1" r:id="rId1"/>
+    <sheet name="監控股票" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>股票名稱</t>
   </si>
   <si>
+    <t>代號</t>
+  </si>
+  <si>
+    <t>買進目標價</t>
+  </si>
+  <si>
+    <t>買進本益比上限</t>
+  </si>
+  <si>
     <t>台積電</t>
   </si>
   <si>
@@ -75,109 +65,209 @@
   </si>
   <si>
     <t>采鈺</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>印能科技</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>新代</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>德律</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>潁威</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>中探針</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>捷創科技</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>聯亞</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>波若威</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>上詮</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>群聯</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>所羅門</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>台特化</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>致茂</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>雷科</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>惠特</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>瑞耘</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>東捷</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>鈦昇</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>友威科</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>大立光</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>達明</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>勤誠</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>代號</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -188,7 +278,15 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="新細明體"/>
-      <family val="1"/>
+      <family val="2"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="新細明體"/>
+      <family val="2"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -200,15 +298,188 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -217,39 +488,289 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="42">
+    <cellStyle name="20% - 輔色1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - 輔色2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - 輔色3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - 輔色4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - 輔色5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - 輔色6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - 輔色1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - 輔色2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - 輔色3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - 輔色4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - 輔色5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - 輔色6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - 輔色1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - 輔色2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - 輔色3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - 輔色4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - 輔色5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - 輔色6" xfId="41" builtinId="52" customBuiltin="1"/>
     <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="中等" xfId="8" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="合計" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="好" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="計算方式" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="連結的儲存格" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="備註" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="說明文字" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="輔色1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="輔色2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="輔色3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="輔色4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="輔色5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="輔色6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="標題" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="標題 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="標題 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="標題 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="標題 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="輸入" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="輸出" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="檢查儲存格" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="壞" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="警告文字" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -580,287 +1101,488 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EA9C9C0-9122-4004-885C-7EC096E82716}">
-  <dimension ref="A1:B34"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04C316D6-CB3C-4F7F-A2AB-7F3858D2356E}">
+  <dimension ref="A1:D34"/>
   <sheetFormatPr defaultRowHeight="15.3" x14ac:dyDescent="0.55000000000000004"/>
-  <cols>
-    <col min="1" max="1" width="22.76171875" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="2" t="s">
         <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" t="s">
+        <v>4</v>
       </c>
       <c r="B2">
         <v>2330</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="2" t="s">
-        <v>2</v>
+      <c r="C2">
+        <v>960</v>
+      </c>
+      <c r="D2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" t="s">
+        <v>5</v>
       </c>
       <c r="B3">
         <v>3017</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="2" t="s">
-        <v>3</v>
+      <c r="C3">
+        <v>850</v>
+      </c>
+      <c r="D3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
+        <v>6</v>
       </c>
       <c r="B4">
         <v>3131</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="2" t="s">
-        <v>4</v>
+      <c r="C4">
+        <v>1350</v>
+      </c>
+      <c r="D4">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" t="s">
+        <v>7</v>
       </c>
       <c r="B5">
         <v>3443</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="2" t="s">
-        <v>5</v>
+      <c r="C5">
+        <v>1050</v>
+      </c>
+      <c r="D5">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" t="s">
+        <v>8</v>
       </c>
       <c r="B6">
         <v>6442</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="2" t="s">
-        <v>6</v>
+      <c r="C6">
+        <v>320</v>
+      </c>
+      <c r="D6">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" t="s">
+        <v>9</v>
       </c>
       <c r="B7">
         <v>3324</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="2" t="s">
-        <v>7</v>
+      <c r="C7">
+        <v>680</v>
+      </c>
+      <c r="D7">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" t="s">
+        <v>10</v>
       </c>
       <c r="B8">
         <v>6510</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="2" t="s">
-        <v>8</v>
+      <c r="C8">
+        <v>520</v>
+      </c>
+      <c r="D8">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" t="s">
+        <v>11</v>
       </c>
       <c r="B9">
         <v>3563</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="2" t="s">
-        <v>9</v>
+      <c r="C9">
+        <v>310</v>
+      </c>
+      <c r="D9">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" t="s">
+        <v>12</v>
       </c>
       <c r="B10">
         <v>7751</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="2" t="s">
-        <v>10</v>
+      <c r="C10">
+        <v>210</v>
+      </c>
+      <c r="D10">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" t="s">
+        <v>13</v>
       </c>
       <c r="B11">
         <v>2308</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="2" t="s">
-        <v>11</v>
+      <c r="C11">
+        <v>340</v>
+      </c>
+      <c r="D11">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" t="s">
+        <v>14</v>
       </c>
       <c r="B12">
         <v>6789</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="2" t="s">
-        <v>12</v>
+      <c r="C12">
+        <v>280</v>
+      </c>
+      <c r="D12">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" t="s">
+        <v>15</v>
       </c>
       <c r="B13">
         <v>7734</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="2" t="s">
-        <v>13</v>
+      <c r="C13">
+        <v>1100</v>
+      </c>
+      <c r="D13">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" t="s">
+        <v>16</v>
       </c>
       <c r="B14">
         <v>7750</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="2" t="s">
-        <v>14</v>
+      <c r="C14">
+        <v>260</v>
+      </c>
+      <c r="D14">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" t="s">
+        <v>17</v>
       </c>
       <c r="B15">
         <v>3030</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="2" t="s">
-        <v>15</v>
+      <c r="C15">
+        <v>135</v>
+      </c>
+      <c r="D15">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" t="s">
+        <v>18</v>
       </c>
       <c r="B16">
         <v>6515</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="2" t="s">
-        <v>16</v>
+      <c r="C16">
+        <v>820</v>
+      </c>
+      <c r="D16">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" t="s">
+        <v>19</v>
       </c>
       <c r="B17">
         <v>6217</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="2" t="s">
-        <v>17</v>
+      <c r="C17">
+        <v>42</v>
+      </c>
+      <c r="D17">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" t="s">
+        <v>20</v>
       </c>
       <c r="B18">
         <v>7810</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="2" t="s">
-        <v>18</v>
+      <c r="C18">
+        <v>195</v>
+      </c>
+      <c r="D18">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" t="s">
+        <v>21</v>
       </c>
       <c r="B19">
         <v>3081</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="2" t="s">
-        <v>19</v>
+      <c r="C19">
+        <v>240</v>
+      </c>
+      <c r="D19">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" t="s">
+        <v>22</v>
       </c>
       <c r="B20">
         <v>3163</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="2" t="s">
-        <v>20</v>
+      <c r="C20">
+        <v>120</v>
+      </c>
+      <c r="D20">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" t="s">
+        <v>23</v>
       </c>
       <c r="B21">
         <v>3363</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="2" t="s">
-        <v>21</v>
+      <c r="C21">
+        <v>160</v>
+      </c>
+      <c r="D21">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" t="s">
+        <v>24</v>
       </c>
       <c r="B22">
         <v>8299</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="2" t="s">
-        <v>22</v>
+      <c r="C22">
+        <v>510</v>
+      </c>
+      <c r="D22">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" t="s">
+        <v>25</v>
       </c>
       <c r="B23">
         <v>2359</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="2" t="s">
-        <v>23</v>
+      <c r="C23">
+        <v>115</v>
+      </c>
+      <c r="D23">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" t="s">
+        <v>26</v>
       </c>
       <c r="B24">
         <v>4772</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="2" t="s">
-        <v>24</v>
+      <c r="C24">
+        <v>140</v>
+      </c>
+      <c r="D24">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" t="s">
+        <v>27</v>
       </c>
       <c r="B25">
         <v>2360</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="2" t="s">
-        <v>25</v>
+      <c r="C25">
+        <v>330</v>
+      </c>
+      <c r="D25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" t="s">
+        <v>28</v>
       </c>
       <c r="B26">
         <v>6207</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="2" t="s">
-        <v>26</v>
+      <c r="C26">
+        <v>65</v>
+      </c>
+      <c r="D26">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" t="s">
+        <v>29</v>
       </c>
       <c r="B27">
         <v>6706</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="2" t="s">
-        <v>27</v>
+      <c r="C27">
+        <v>130</v>
+      </c>
+      <c r="D27">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" t="s">
+        <v>30</v>
       </c>
       <c r="B28">
         <v>6532</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="2" t="s">
-        <v>28</v>
+      <c r="C28">
+        <v>75</v>
+      </c>
+      <c r="D28">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" t="s">
+        <v>31</v>
       </c>
       <c r="B29">
         <v>8064</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="2" t="s">
-        <v>29</v>
+      <c r="C29">
+        <v>48</v>
+      </c>
+      <c r="D29">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" t="s">
+        <v>32</v>
       </c>
       <c r="B30">
         <v>8027</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="2" t="s">
-        <v>30</v>
+      <c r="C30">
+        <v>80</v>
+      </c>
+      <c r="D30">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" t="s">
+        <v>33</v>
       </c>
       <c r="B31">
         <v>3580</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="2" t="s">
-        <v>31</v>
+      <c r="C31">
+        <v>72</v>
+      </c>
+      <c r="D31">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" t="s">
+        <v>34</v>
       </c>
       <c r="B32">
         <v>3008</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="2" t="s">
-        <v>32</v>
+      <c r="C32">
+        <v>2100</v>
+      </c>
+      <c r="D32">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" t="s">
+        <v>35</v>
       </c>
       <c r="B33">
         <v>4585</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="2" t="s">
-        <v>33</v>
+      <c r="C33">
+        <v>180</v>
+      </c>
+      <c r="D33">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" t="s">
+        <v>36</v>
       </c>
       <c r="B34">
         <v>8210</v>
       </c>
+      <c r="C34">
+        <v>260</v>
+      </c>
+      <c r="D34">
+        <v>16</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/監控股票.xlsx
+++ b/data/監控股票.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ihsiangtsou-my.sharepoint.com/personal/yihshan_ihsiangtsou_onmicrosoft_com/Documents/GitHub/stock-dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7DB10D0E-727A-4EEA-B726-C4DEB2E7E2B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{7DB10D0E-727A-4EEA-B726-C4DEB2E7E2B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{04A00A79-3C15-4D65-8C69-AE7804000537}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="2715" windowWidth="29040" windowHeight="15720" xr2:uid="{8896E701-D4C2-4EA3-A0CB-CC938DEDCC47}"/>
   </bookViews>
@@ -1127,7 +1127,7 @@
         <v>2330</v>
       </c>
       <c r="C2">
-        <v>960</v>
+        <v>2000</v>
       </c>
       <c r="D2">
         <v>18</v>

--- a/data/監控股票.xlsx
+++ b/data/監控股票.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ihsiangtsou-my.sharepoint.com/personal/yihshan_ihsiangtsou_onmicrosoft_com/Documents/GitHub/stock-dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{7DB10D0E-727A-4EEA-B726-C4DEB2E7E2B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{04A00A79-3C15-4D65-8C69-AE7804000537}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{7DB10D0E-727A-4EEA-B726-C4DEB2E7E2B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4247208F-E3EC-4E53-9F98-87FF24A6F50A}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="2715" windowWidth="29040" windowHeight="15720" xr2:uid="{8896E701-D4C2-4EA3-A0CB-CC938DEDCC47}"/>
   </bookViews>
@@ -783,6 +783,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/監控股票.xlsx
+++ b/data/監控股票.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ihsiangtsou-my.sharepoint.com/personal/yihshan_ihsiangtsou_onmicrosoft_com/Documents/GitHub/stock-dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{7DB10D0E-727A-4EEA-B726-C4DEB2E7E2B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4247208F-E3EC-4E53-9F98-87FF24A6F50A}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="8_{7DB10D0E-727A-4EEA-B726-C4DEB2E7E2B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F90EAEA3-8B99-4891-B797-8184F8ED1DB0}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="2715" windowWidth="29040" windowHeight="15720" xr2:uid="{8896E701-D4C2-4EA3-A0CB-CC938DEDCC47}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>股票名稱</t>
   </si>
@@ -131,6 +131,14 @@
   </si>
   <si>
     <t>勤誠</t>
+  </si>
+  <si>
+    <t>國巨</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>九豪</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1106,8 +1114,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04C316D6-CB3C-4F7F-A2AB-7F3858D2356E}">
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr defaultRowHeight="15.3" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="3" max="3" width="13" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
@@ -1583,6 +1594,22 @@
       </c>
       <c r="D34">
         <v>16</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35">
+        <v>2327</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36">
+        <v>6127</v>
       </c>
     </row>
   </sheetData>

--- a/data/監控股票.xlsx
+++ b/data/監控股票.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ihsiangtsou-my.sharepoint.com/personal/yihshan_ihsiangtsou_onmicrosoft_com/Documents/GitHub/stock-dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0D86CE82-9F5C-404C-B0C7-1B926DDF7227}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="8_{0D86CE82-9F5C-404C-B0C7-1B926DDF7227}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AFCB0DB7-1EF8-4D5A-A340-AB2272B43760}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="2715" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="49">
   <si>
     <t>股票名稱</t>
   </si>
@@ -149,13 +149,37 @@
   </si>
   <si>
     <t>九豪</t>
+  </si>
+  <si>
+    <t>預估每股配息</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>元大高股息</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>群益台灣精選高息</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0056</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>00919</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ETF</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -173,6 +197,33 @@
       <name val="Arial"/>
       <family val="3"/>
       <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft JhengHei"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -196,9 +247,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -214,6 +270,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -417,10 +477,10 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
-  <sheetFormatPr defaultColWidth="12.609375" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:H38"/>
+  <sheetFormatPr defaultColWidth="12.609375" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -442,8 +502,11 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="H1" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -466,7 +529,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -489,7 +552,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:8" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -512,7 +575,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:8" ht="15.75" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -535,7 +598,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:8" ht="15.75" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
@@ -558,7 +621,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:8" ht="15.75" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
@@ -581,7 +644,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:8" ht="15.75" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -604,7 +667,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:8" ht="15.75" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
@@ -627,7 +690,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:8" ht="15.75" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
@@ -650,7 +713,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:8" ht="15.75" customHeight="1">
       <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
@@ -673,7 +736,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:8" ht="15.75" customHeight="1">
       <c r="A12" s="1" t="s">
         <v>18</v>
       </c>
@@ -696,7 +759,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:8" ht="15.75" customHeight="1">
       <c r="A13" s="1" t="s">
         <v>19</v>
       </c>
@@ -719,7 +782,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:8" ht="15.75" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>20</v>
       </c>
@@ -742,7 +805,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:8" ht="15.75" customHeight="1">
       <c r="A15" s="1" t="s">
         <v>21</v>
       </c>
@@ -765,7 +828,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:8" ht="15.75" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>22</v>
       </c>
@@ -788,7 +851,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:7" ht="15.75" customHeight="1">
       <c r="A17" s="1" t="s">
         <v>23</v>
       </c>
@@ -811,7 +874,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:7" ht="15.75" customHeight="1">
       <c r="A18" s="1" t="s">
         <v>24</v>
       </c>
@@ -834,7 +897,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:7" ht="15.75" customHeight="1">
       <c r="A19" s="1" t="s">
         <v>25</v>
       </c>
@@ -857,7 +920,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:7" ht="15.75" customHeight="1">
       <c r="A20" s="1" t="s">
         <v>26</v>
       </c>
@@ -880,7 +943,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:7" ht="15.75" customHeight="1">
       <c r="A21" s="1" t="s">
         <v>27</v>
       </c>
@@ -903,7 +966,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:7" ht="15.75" customHeight="1">
       <c r="A22" s="1" t="s">
         <v>28</v>
       </c>
@@ -926,7 +989,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:7" ht="15.75" customHeight="1">
       <c r="A23" s="1" t="s">
         <v>29</v>
       </c>
@@ -949,7 +1012,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:7" ht="15.75" customHeight="1">
       <c r="A24" s="1" t="s">
         <v>30</v>
       </c>
@@ -972,7 +1035,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:7" ht="15.75" customHeight="1">
       <c r="A25" s="1" t="s">
         <v>31</v>
       </c>
@@ -995,7 +1058,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:7" ht="15.75" customHeight="1">
       <c r="A26" s="1" t="s">
         <v>32</v>
       </c>
@@ -1018,7 +1081,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:7" ht="15.75" customHeight="1">
       <c r="A27" s="1" t="s">
         <v>33</v>
       </c>
@@ -1041,7 +1104,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:7" ht="15.75" customHeight="1">
       <c r="A28" s="1" t="s">
         <v>34</v>
       </c>
@@ -1064,7 +1127,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:7" ht="15.75" customHeight="1">
       <c r="A29" s="1" t="s">
         <v>35</v>
       </c>
@@ -1087,7 +1150,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:7" ht="15.75" customHeight="1">
       <c r="A30" s="1" t="s">
         <v>36</v>
       </c>
@@ -1110,7 +1173,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:7" ht="15.75" customHeight="1">
       <c r="A31" s="1" t="s">
         <v>37</v>
       </c>
@@ -1133,7 +1196,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:7" ht="15.75" customHeight="1">
       <c r="A32" s="1" t="s">
         <v>38</v>
       </c>
@@ -1156,7 +1219,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:8" ht="15.75" customHeight="1">
       <c r="A33" s="1" t="s">
         <v>39</v>
       </c>
@@ -1179,7 +1242,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:8" ht="15.75" customHeight="1">
       <c r="A34" s="1" t="s">
         <v>40</v>
       </c>
@@ -1202,7 +1265,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:8" ht="15.75" customHeight="1">
       <c r="A35" s="1" t="s">
         <v>41</v>
       </c>
@@ -1225,7 +1288,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:8" ht="15.75" customHeight="1">
       <c r="A36" s="1" t="s">
         <v>42</v>
       </c>
@@ -1246,6 +1309,34 @@
       </c>
       <c r="G36" s="1">
         <v>15</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A37" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H37">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A38" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H38">
+        <v>3.74</v>
       </c>
     </row>
   </sheetData>

--- a/data/監控股票.xlsx
+++ b/data/監控股票.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ihsiangtsou-my.sharepoint.com/personal/yihshan_ihsiangtsou_onmicrosoft_com/Documents/GitHub/stock-dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="8_{0D86CE82-9F5C-404C-B0C7-1B926DDF7227}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AFCB0DB7-1EF8-4D5A-A340-AB2272B43760}"/>
+  <xr:revisionPtr revIDLastSave="41" documentId="8_{0D86CE82-9F5C-404C-B0C7-1B926DDF7227}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B03DB8D2-2727-49B9-B85A-399F4CDE1214}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="2715" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -528,6 +528,9 @@
       <c r="G2" s="1">
         <v>18</v>
       </c>
+      <c r="H2" s="4">
+        <v>28</v>
+      </c>
     </row>
     <row r="3" spans="1:8" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
@@ -551,6 +554,9 @@
       <c r="G3" s="1">
         <v>22</v>
       </c>
+      <c r="H3" s="4">
+        <v>21</v>
+      </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
@@ -574,6 +580,9 @@
       <c r="G4" s="1">
         <v>25</v>
       </c>
+      <c r="H4" s="4">
+        <v>46.225000000000001</v>
+      </c>
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1">
       <c r="A5" s="1" t="s">
@@ -597,6 +606,9 @@
       <c r="G5" s="1">
         <v>25</v>
       </c>
+      <c r="H5" s="4">
+        <v>20</v>
+      </c>
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1">
       <c r="A6" s="1" t="s">
@@ -620,6 +632,9 @@
       <c r="G6" s="1">
         <v>28</v>
       </c>
+      <c r="H6" s="4">
+        <v>11.259</v>
+      </c>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1">
       <c r="A7" s="1" t="s">
@@ -643,6 +658,9 @@
       <c r="G7" s="1">
         <v>22</v>
       </c>
+      <c r="H7" s="4">
+        <v>11.903</v>
+      </c>
     </row>
     <row r="8" spans="1:8" ht="15.75" customHeight="1">
       <c r="A8" s="1" t="s">
@@ -666,6 +684,9 @@
       <c r="G8" s="1">
         <v>25</v>
       </c>
+      <c r="H8" s="4">
+        <v>15.234999999999999</v>
+      </c>
     </row>
     <row r="9" spans="1:8" ht="15.75" customHeight="1">
       <c r="A9" s="1" t="s">
@@ -689,6 +710,9 @@
       <c r="G9" s="1">
         <v>20</v>
       </c>
+      <c r="H9" s="4">
+        <v>12</v>
+      </c>
     </row>
     <row r="10" spans="1:8" ht="15.75" customHeight="1">
       <c r="A10" s="1" t="s">
@@ -712,6 +736,9 @@
       <c r="G10" s="1">
         <v>25</v>
       </c>
+      <c r="H10" s="4">
+        <v>18</v>
+      </c>
     </row>
     <row r="11" spans="1:8" ht="15.75" customHeight="1">
       <c r="A11" s="1" t="s">
@@ -735,6 +762,9 @@
       <c r="G11" s="1">
         <v>18</v>
       </c>
+      <c r="H11" s="4">
+        <v>11.6</v>
+      </c>
     </row>
     <row r="12" spans="1:8" ht="15.75" customHeight="1">
       <c r="A12" s="1" t="s">
@@ -758,6 +788,9 @@
       <c r="G12" s="1">
         <v>22</v>
       </c>
+      <c r="H12" s="4">
+        <v>3</v>
+      </c>
     </row>
     <row r="13" spans="1:8" ht="15.75" customHeight="1">
       <c r="A13" s="1" t="s">
@@ -781,6 +814,9 @@
       <c r="G13" s="1">
         <v>25</v>
       </c>
+      <c r="H13" s="4">
+        <v>19.850999999999999</v>
+      </c>
     </row>
     <row r="14" spans="1:8" ht="15.75" customHeight="1">
       <c r="A14" s="1" t="s">
@@ -804,6 +840,9 @@
       <c r="G14" s="1">
         <v>22</v>
       </c>
+      <c r="H14" s="4">
+        <v>16</v>
+      </c>
     </row>
     <row r="15" spans="1:8" ht="15.75" customHeight="1">
       <c r="A15" s="1" t="s">
@@ -850,8 +889,11 @@
       <c r="G16" s="1">
         <v>18</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" ht="15.75" customHeight="1">
+      <c r="H16" s="4">
+        <v>49.438000000000002</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="15.75" customHeight="1">
       <c r="A17" s="1" t="s">
         <v>23</v>
       </c>
@@ -873,8 +915,11 @@
       <c r="G17" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" ht="15.75" customHeight="1">
+      <c r="H17" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="15.75" customHeight="1">
       <c r="A18" s="1" t="s">
         <v>24</v>
       </c>
@@ -897,7 +942,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="15.75" customHeight="1">
+    <row r="19" spans="1:8" ht="15.75" customHeight="1">
       <c r="A19" s="1" t="s">
         <v>25</v>
       </c>
@@ -919,8 +964,11 @@
       <c r="G19" s="1">
         <v>30</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" ht="15.75" customHeight="1">
+      <c r="H19" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="15.75" customHeight="1">
       <c r="A20" s="1" t="s">
         <v>26</v>
       </c>
@@ -942,8 +990,11 @@
       <c r="G20" s="1">
         <v>18</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" ht="15.75" customHeight="1">
+      <c r="H20" s="4">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="15.75" customHeight="1">
       <c r="A21" s="1" t="s">
         <v>27</v>
       </c>
@@ -965,8 +1016,11 @@
       <c r="G21" s="1">
         <v>30</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" ht="15.75" customHeight="1">
+      <c r="H21" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="15.75" customHeight="1">
       <c r="A22" s="1" t="s">
         <v>28</v>
       </c>
@@ -988,8 +1042,11 @@
       <c r="G22" s="1">
         <v>12</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" ht="15.75" customHeight="1">
+      <c r="H22" s="4">
+        <v>23.192</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="15.75" customHeight="1">
       <c r="A23" s="1" t="s">
         <v>29</v>
       </c>
@@ -1011,8 +1068,11 @@
       <c r="G23" s="1">
         <v>25</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" ht="15.75" customHeight="1">
+      <c r="H23" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="15.75" customHeight="1">
       <c r="A24" s="1" t="s">
         <v>30</v>
       </c>
@@ -1035,7 +1095,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="15.75" customHeight="1">
+    <row r="25" spans="1:8" ht="15.75" customHeight="1">
       <c r="A25" s="1" t="s">
         <v>31</v>
       </c>
@@ -1057,8 +1117,11 @@
       <c r="G25" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" ht="15.75" customHeight="1">
+      <c r="H25" s="4">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="15.75" customHeight="1">
       <c r="A26" s="1" t="s">
         <v>32</v>
       </c>
@@ -1080,8 +1143,11 @@
       <c r="G26" s="1">
         <v>15</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" ht="15.75" customHeight="1">
+      <c r="H26" s="4">
+        <v>0.60299999999999998</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="15.75" customHeight="1">
       <c r="A27" s="1" t="s">
         <v>33</v>
       </c>
@@ -1103,8 +1169,11 @@
       <c r="G27" s="1">
         <v>25</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" ht="15.75" customHeight="1">
+      <c r="H27" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="15.75" customHeight="1">
       <c r="A28" s="1" t="s">
         <v>34</v>
       </c>
@@ -1126,8 +1195,11 @@
       <c r="G28" s="1">
         <v>16</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" ht="15.75" customHeight="1">
+      <c r="H28" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="15.75" customHeight="1">
       <c r="A29" s="1" t="s">
         <v>35</v>
       </c>
@@ -1149,8 +1221,11 @@
       <c r="G29" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" ht="15.75" customHeight="1">
+      <c r="H29" s="4">
+        <v>0.98099999999999998</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="15.75" customHeight="1">
       <c r="A30" s="1" t="s">
         <v>36</v>
       </c>
@@ -1172,8 +1247,11 @@
       <c r="G30" s="1">
         <v>18</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" ht="15.75" customHeight="1">
+      <c r="H30" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="15.75" customHeight="1">
       <c r="A31" s="1" t="s">
         <v>37</v>
       </c>
@@ -1195,8 +1273,11 @@
       <c r="G31" s="1">
         <v>16</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" ht="15.75" customHeight="1">
+      <c r="H31" s="4">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="15.75" customHeight="1">
       <c r="A32" s="1" t="s">
         <v>38</v>
       </c>
@@ -1217,6 +1298,9 @@
       </c>
       <c r="G32" s="1">
         <v>14</v>
+      </c>
+      <c r="H32" s="4">
+        <v>80</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="15.75" customHeight="1">
@@ -1240,6 +1324,9 @@
       </c>
       <c r="G33" s="1">
         <v>25</v>
+      </c>
+      <c r="H33" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="15.75" customHeight="1">
